--- a/docs/data/kpi_export.xlsx
+++ b/docs/data/kpi_export.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20 23:49 UTC</t>
+          <t>2026-09-21 04:12 UTC</t>
         </is>
       </c>
     </row>
